--- a/docs/map-label-bang-cot-ahs.xlsx
+++ b/docs/map-label-bang-cot-ahs.xlsx
@@ -28,25 +28,25 @@
     <sheet name="AHS_BICANBICAO_HISTORY" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AHS_VUAN'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AHS_SOTHAM_BANAN'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AHS_SOTHAM_QUYETDINH_VUAN'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AHS_CHUYEN_NHAN_AN'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AHS_VUAN_GIAIDOAN'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AHS_SOTHAM_THULY'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHS_SOTHAM_KHANGCAO'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AHS_SOTHAM_KHANGCAO_YEUCAU'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AHS_SOTHAM_KHANGNGHI'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AHS_SOTHAM_KHANGNGHI_YEUCAU'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AHS_BICANBICAO'!$A$1:$G$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AHS_BICAN_NHANTHAN'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AHS_SOTHAM_BIENPHAPNGANCHAN'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AHS_SOTHAM_CAOTRANG_DIEULUAT'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AHS_SOTHAM_BANAN_BICAO'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AHS_SOTHAM_BANAN_DIEU_CHITIET'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AHS_NGUOITHAMGIATOTUNG'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'AHS_NGUOITHAMGIATOTUNG_TUCACH'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AHS_BICANBICAO_HISTORY'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AHS_VUAN'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AHS_SOTHAM_BANAN'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AHS_SOTHAM_QUYETDINH_VUAN'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AHS_CHUYEN_NHAN_AN'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AHS_VUAN_GIAIDOAN'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'AHS_SOTHAM_THULY'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AHS_SOTHAM_KHANGCAO'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'AHS_SOTHAM_KHANGCAO_YEUCAU'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'AHS_SOTHAM_KHANGNGHI'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'AHS_SOTHAM_KHANGNGHI_YEUCAU'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'AHS_BICANBICAO'!$A$1:$K$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'AHS_BICAN_NHANTHAN'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'AHS_SOTHAM_BIENPHAPNGANCHAN'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'AHS_SOTHAM_CAOTRANG_DIEULUAT'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'AHS_SOTHAM_BANAN_BICAO'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'AHS_SOTHAM_BANAN_DIEU_CHITIET'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'AHS_NGUOITHAMGIATOTUNG'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'AHS_NGUOITHAMGIATOTUNG_TUCACH'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'AHS_BICANBICAO_HISTORY'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,6 +518,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -547,6 +571,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -584,6 +616,26 @@
           <t>SelectedIndex</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded truong hop thu ly phuc tham</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0=Do co KC/KN; 1=Thu ly lai xet xu PT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -621,6 +673,26 @@
           <t>Chi set khi tao moi</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN via DM_TOAAN_BL.DM_TOAAN_GETBY_PARENT; SP PKG_STPT.DM_TOAAN_GETBY_PARENT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Params: V_CAPXX=3, V_DONVIID=Session DONVIID, V_LOAITOA=Session CAP_XET_XU; remove current court</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -658,6 +730,14 @@
           <t>So tham -&gt; Phuc tham</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -695,6 +775,26 @@
           <t>Set bang don vi dang nhap</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -732,6 +832,14 @@
           <t>Set 2 khi tao moi</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -765,6 +873,26 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>TRUONGHOP_GIAONHAN / ENUM_AHS_TRANGTHAIGIAONHAN_HS</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Mostly hardcoded; sometimes DM_DATAITEM by saved ID</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1=VKS giao HS xu so tham; 2=VKS chap nhan dieu tra bo sung (comment); 3=VKS khong chap nhan dieu tra bo sung (comment); 270=Xet xu lai cap so tham</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -798,6 +926,26 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>QUYETDINHCAOTRANG</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.QUYETDINHCAOTRANG</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -831,6 +979,14 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -868,6 +1024,14 @@
           <t>Parse dd/MM/yyyy</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -901,6 +1065,14 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -934,6 +1106,14 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -971,6 +1151,14 @@
           <t>Tu sinh khi tao moi</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1004,6 +1192,14 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1037,6 +1233,14 @@
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1070,6 +1274,14 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1103,6 +1315,14 @@
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1140,6 +1360,14 @@
           <t>Lay tu ngay xay ra</t>
         </is>
       </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1177,6 +1405,14 @@
           <t>Lay tu ngay xay ra</t>
         </is>
       </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1210,6 +1446,26 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded gio</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded loop in LoadCombobox()</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>00..23</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1247,6 +1503,14 @@
           <t>Tinh lai tu danh sach bi can</t>
         </is>
       </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1284,9 +1548,17 @@
           <t>Tinh lai tu tinh trang giam giu</t>
         </is>
       </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1297,7 +1569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1307,6 +1579,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1345,6 +1621,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1382,6 +1678,14 @@
           <t>FK AHS_SOTHAM_KHANGNGHI.ID</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1419,9 +1723,29 @@
           <t>Moi checkbox duoc chon tao/cap nhat 1 dong</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YEUCAUKNHINHSU</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.YEUCAUKNHINHSU</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1432,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1766,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1480,6 +1808,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1517,6 +1865,14 @@
           <t>URL hsID=326049</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1554,6 +1910,26 @@
           <t>0 ca nhan, 1/2 phap nhan</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded doi tuong pham toi</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0=Ca nhan; 1=Phap nhan thuong mai; 2=Phap nhan phi thuong mai</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,6 +1967,26 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1628,6 +2024,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1661,6 +2077,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1694,6 +2118,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1727,6 +2159,14 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1760,6 +2200,14 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1793,6 +2241,14 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1830,6 +2286,14 @@
           <t>1/0</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1867,6 +2331,14 @@
           <t>2 neu user xac nhan khong lam sach duoc</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1900,6 +2372,26 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>QUOCTICH</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.QUOCTICH; default GetQuocTichID_VN()</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1933,6 +2425,26 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>DANTOC</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.DANTOC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1966,6 +2478,26 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>TONGIAO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.TONGIAO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1999,6 +2531,26 @@
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded gioi tinh</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in .aspx</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>pBiCao: 0=Chon, 1=Nam, 2=Nu; pNguoiThamGiaTT: 1=Nam, 0=Nu</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2032,6 +2584,14 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2069,6 +2629,14 @@
           <t>Lay tu ngay sinh</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2102,6 +2670,14 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2135,6 +2711,26 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2168,6 +2764,26 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2201,6 +2817,14 @@
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2234,6 +2858,26 @@
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH tinh</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=ROOT; default LoginTinhID</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2267,6 +2911,26 @@
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH huyen/xa</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=selected tinh</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2304,6 +2968,14 @@
           <t>Ten cot trong code la KHTTCHITIET</t>
         </is>
       </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2337,6 +3009,26 @@
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH tinh</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=ROOT; default LoginTinhID</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2370,6 +3062,26 @@
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH huyen/xa</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=selected tinh</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2403,6 +3115,14 @@
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2436,6 +3156,26 @@
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>TRINHDOVANHOA</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.TRINHDOVANHOA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2469,6 +3209,26 @@
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>TINHTRANGGIAMGIU</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.TINHTRANGGIAMGIU</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2502,6 +3262,26 @@
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in .aspx</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2535,6 +3315,26 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2568,6 +3368,26 @@
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2601,6 +3421,26 @@
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2634,6 +3474,26 @@
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2667,6 +3527,26 @@
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2700,6 +3580,14 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2733,6 +3621,14 @@
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2766,6 +3662,26 @@
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2799,6 +3715,26 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2832,6 +3768,26 @@
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2865,6 +3821,26 @@
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2898,6 +3874,14 @@
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2931,6 +3915,14 @@
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2964,6 +3956,26 @@
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>NGHENGHIEP</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.NGHENGHIEP</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2997,6 +4009,26 @@
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded dia ban pham toi</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>blank=--Chon--; 0=Nong thon; 1=Thanh thi; 2=Mien nui/vung sau/vung xa/hai dao/khac</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3030,6 +4062,14 @@
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3067,6 +4107,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3104,6 +4152,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH tinh</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=ROOT</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3141,6 +4209,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH huyen/xa</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=selected tinh</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3178,6 +4266,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3215,6 +4311,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH tinh</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=ROOT</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3252,6 +4368,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH huyen/xa</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>DM_HANHCHINH via GSTPContext; filter CAPCHAID parent; text TEN, value ID</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Filter CAPCHAID=selected tinh</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3289,6 +4425,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3326,6 +4470,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3363,6 +4515,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3400,6 +4560,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3437,6 +4617,26 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pBiCao.aspx</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3474,6 +4674,14 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3511,9 +4719,17 @@
           <t>Phap nhan</t>
         </is>
       </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G60"/>
+  <autoFilter ref="A1:K60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3524,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3534,6 +4750,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3572,6 +4792,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3605,6 +4845,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3642,6 +4890,26 @@
           <t>FK AHS_BICANBICAO.ID</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3679,6 +4947,14 @@
           <t>Bo/Me/Vo chong/Con</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3712,6 +4988,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3745,6 +5029,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3778,6 +5070,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3811,9 +5111,17 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3824,7 +5132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3834,6 +5142,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3872,6 +5184,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3905,6 +5237,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3938,6 +5278,26 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3971,6 +5331,26 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>BIENPHAPNGANCHAN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.BIENPHAPNGANCHAN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4004,6 +5384,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>LOAIDONVIQDNGANCHAN</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.LOAIDONVIQDNGANCHAN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4041,6 +5441,26 @@
           <t>Set 1</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded fixed value</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Code assignment</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ISHOSO=1 / HIEULUC=1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4074,6 +5494,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4107,9 +5535,17 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4120,7 +5556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4130,6 +5566,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4168,6 +5608,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4201,6 +5661,26 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4234,6 +5714,14 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4267,6 +5755,26 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_BOLUAT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Filter HIEULUC=1 and LOAI=AN_HINHSU</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4300,6 +5808,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Used for TOIDANHID/TENTOIDANH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4333,6 +5861,26 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Used for TOIDANHID/TENTOIDANH</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4366,6 +5914,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4399,6 +5955,14 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4432,6 +5996,26 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4465,6 +6049,26 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_BOLUAT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Filter HIEULUC=1 and LOAI=AN_HINHSU</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4502,6 +6106,26 @@
           <t>Nhap de tim toi danh</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Lookup/search in DM_BOLUAT_TOIDANH after choosing DM_BOLUAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>User enters Dieu/Khoan/Diem to find TOIDANHID; values are not stored directly in mapped column</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4535,6 +6159,26 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_BOLUAT_TOIDANH</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Used for TOIDANHID/TENTOIDANH</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4568,9 +6212,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4581,7 +6233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4591,6 +6243,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4629,6 +6285,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4666,6 +6342,26 @@
           <t>Tu dong tao khi copy toi danh cao trang sang ban an</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AHS_SOTHAM_BANAN</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext AHS_SOTHAM_BANAN</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Parent ban an row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4699,9 +6395,29 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4712,7 +6428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4722,6 +6438,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4760,6 +6480,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4793,6 +6533,26 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AHS_SOTHAM_BANAN</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext AHS_SOTHAM_BANAN</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Parent ban an row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4826,6 +6586,26 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>AHS_BICANBICAO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Parent/FK from saved bi can</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>FK to AHS_BICANBICAO.ID</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4859,6 +6639,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4892,6 +6680,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4925,6 +6721,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4958,6 +6762,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4991,9 +6803,17 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5004,7 +6824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5014,6 +6834,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5052,6 +6876,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5089,6 +6933,14 @@
           <t>URL hsID=326049</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5126,6 +6978,26 @@
           <t>0 ca nhan, 1 co quan, 2 to chuc</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded doi tuong TGTT</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pNguoiThamGiaTT.aspx</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0=Ca nhan; 1=Co quan; 2=To chuc</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5159,6 +7031,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5192,6 +7072,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5229,6 +7117,26 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded gioi tinh</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in .aspx</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>pBiCao: 0=Chon, 1=Nam, 2=Nu; pNguoiThamGiaTT: 1=Nam, 0=Nu</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5266,6 +7174,14 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5303,6 +7219,14 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5340,6 +7264,26 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>NGHENGHIEP</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.NGHENGHIEP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5377,6 +7321,14 @@
           <t>Ca nhan</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5414,6 +7366,26 @@
           <t>Khi tu cach bi hai</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded yes/no</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in .aspx</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5451,6 +7423,26 @@
           <t>Khi tre vi thanh nien</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded phan loai do tuoi</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in pNguoiThamGiaTT.aspx</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1=Duoi 16 tuoi; 2=Duoi 16 tuoi bi ton thuong nghiem trong ve tam ly; 3=Tu du 16 den duoi 18; 4=Tu du 16 den duoi 18 bi ton thuong nghiem trong ve tam ly</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5488,6 +7480,14 @@
           <t>Co quan/to chuc</t>
         </is>
       </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5525,6 +7525,14 @@
           <t>Co quan/to chuc</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5562,6 +7570,14 @@
           <t>Co quan/to chuc</t>
         </is>
       </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5599,6 +7615,14 @@
           <t>Co quan/to chuc</t>
         </is>
       </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5636,6 +7660,14 @@
           <t>Co quan/to chuc</t>
         </is>
       </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5673,9 +7705,29 @@
           <t>Set 1</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded fixed value</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Code assignment</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>ISHOSO=1 / HIEULUC=1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5686,7 +7738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5696,6 +7748,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5734,6 +7790,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5771,6 +7847,14 @@
           <t>FK AHS_NGUOITHAMGIATOTUNG.ID</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5804,9 +7888,29 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>TUCACHTGTTHS</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.TUCACHTGTTHS; special BIHAI=MA TGTTHS_01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5817,7 +7921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5827,6 +7931,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5865,6 +7973,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5902,9 +8030,17 @@
           <t>Serialize object bi can cu va goi BL insert lich su</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5915,7 +8051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5925,6 +8061,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5963,6 +8103,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5996,6 +8156,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6029,6 +8197,14 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6062,6 +8238,26 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN via DM_TOAAN_BL.DM_TOAAN_GETBY_PARENT; SP PKG_STPT.DM_TOAAN_GETBY_PARENT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Params: V_CAPXX=3, V_DONVIID=Session DONVIID, V_LOAITOA=Session CAP_XET_XU; remove current court</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6095,6 +8291,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6128,9 +8332,17 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6141,7 +8353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6151,6 +8363,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6189,6 +8405,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6222,6 +8458,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6255,6 +8499,26 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>DM_QD_QUYETDINH / DM_QD_LOAI</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_QD_LOAI + DM_QD_QUYETDINH</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Filter DM_QD_LOAI.MA=DC, HIEULUC=1, ISHINHSU=1; DM_QD_QUYETDINH.LOAIID=LoaiQD, ISHINHSU=1, ISSOTHAM=1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6292,6 +8556,26 @@
           <t>Lay tu DM_QD_QUYETDINH.LOAIID</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DM_QD_QUYETDINH / DM_QD_LOAI</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext DM_QD_LOAI + DM_QD_QUYETDINH</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Filter DM_QD_LOAI.MA=DC, HIEULUC=1, ISHINHSU=1; DM_QD_QUYETDINH.LOAIID=LoaiQD, ISHINHSU=1, ISSOTHAM=1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6325,6 +8609,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN via DM_TOAAN_BL.DM_TOAAN_GETBY_PARENT; SP PKG_STPT.DM_TOAAN_GETBY_PARENT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Params: V_CAPXX=3, V_DONVIID=Session DONVIID, V_LOAITOA=Session CAP_XET_XU; remove current court</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6358,6 +8662,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6391,6 +8703,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6424,9 +8744,17 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6437,7 +8765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6447,6 +8775,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6485,6 +8817,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6518,6 +8870,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6555,6 +8915,26 @@
           <t>Toa so tham</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN via DM_TOAAN_BL.DM_TOAAN_GETBY_PARENT; SP PKG_STPT.DM_TOAAN_GETBY_PARENT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Params: V_CAPXX=3, V_DONVIID=Session DONVIID, V_LOAITOA=Session CAP_XET_XU; remove current court</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6588,6 +8968,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6621,6 +9009,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6658,6 +9066,14 @@
           <t>DateTime.Now</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6695,6 +9111,14 @@
           <t>Code hien khong lay textbox, set DateTime.Now</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6728,6 +9152,26 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>DM_CANBO Thu ky/TTV</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>DM_CANBO via DM_CANBO_BL.GET_ThuKy_TTVS_CV; SP PKG_STPT.DM_CANBO_GETALLTHUKY_TTV_CV</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Param VDONVIID=Session DONVIID; text MA_TEN, value ID</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6761,6 +9205,14 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6798,6 +9250,26 @@
           <t>267/268/269/998/0 theo KC/KN va thu ly</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>TRUONGHOP_GIAONHAN</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Code conditional + DM_DATAITEM group</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>267/268/269/998/0 based on KC/KN/thu ly</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6835,9 +9307,29 @@
           <t>Set 1 = Nhan</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded trang thai</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Code assignment</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>TRANGTHAI=1 (Nhan)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6848,7 +9340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6858,6 +9350,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6896,6 +9392,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6929,6 +9445,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6966,6 +9490,14 @@
           <t>2 So tham, 3 Phuc tham</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6999,6 +9531,26 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN via DM_TOAAN_BL.DM_TOAAN_GETBY_PARENT; SP PKG_STPT.DM_TOAAN_GETBY_PARENT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Params: V_CAPXX=3, V_DONVIID=Session DONVIID, V_LOAITOA=Session CAP_XET_XU; remove current court</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7032,6 +9584,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7065,6 +9637,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7102,6 +9682,14 @@
           <t>Set 2</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7135,9 +9723,29 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7148,7 +9756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7158,6 +9766,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7196,6 +9808,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7229,6 +9861,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7262,6 +9902,26 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>TRUONGHOPTHULYAN</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.TRUONGHOPTHULYAN; hardcode logic: 233, 236, 1777</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7295,6 +9955,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7328,6 +9996,14 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7365,6 +10041,14 @@
           <t>Bang ngay thu ly</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7398,6 +10082,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7435,6 +10127,26 @@
           <t>Khi thu ly xet xu lai</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>NOIDUNGTHULYXXL</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.NOIDUNGTHULYXXL; 2244=Khac</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7472,6 +10184,14 @@
           <t>Khi noi dung = Khac</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7509,6 +10229,14 @@
           <t>Khi truong hop 233</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7546,9 +10274,17 @@
           <t>Khi truong hop 233</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7559,7 +10295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7569,6 +10305,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7607,6 +10347,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7640,6 +10400,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7673,6 +10441,26 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded loai nguoi khang cao</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0=Bi cao; 1=Khac</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7706,6 +10494,14 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7739,6 +10535,26 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded loai khang cao</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0=Ban an; 1=Quyet dinh</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7772,6 +10588,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7805,6 +10629,26 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded khang cao qua han</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0=Khong; 1=Co</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7842,6 +10686,26 @@
           <t>ID ban an/quyet dinh duoc chon</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>AHS_SOTHAM_BANAN or AHS_SOTHAM_QUYETDINH_VUAN</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext / AHS_SOTHAM_BL.AHS_ST_QD_VUAN_GETLIST</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>If rdbLoaiKC=0 load AHS_SOTHAM_BANAN by VUANID; if 1 load quyet dinh vu an</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7879,6 +10743,14 @@
           <t>Readonly</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7916,6 +10788,26 @@
           <t>Lay tu AHS_VUAN.TOAANID</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7949,9 +10841,17 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7962,7 +10862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7972,6 +10872,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8010,6 +10914,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8047,6 +10971,14 @@
           <t>FK AHS_SOTHAM_KHANGCAO.ID</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8084,9 +11016,29 @@
           <t>Moi checkbox duoc chon tao/cap nhat 1 dong</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YEUCAUKCHINHSU</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>DM_DATAITEM via DM_DATAITEM_BL.DM_DATAITEM_GETBYGROUPNAME(group); SP DM_DATAITEM_GETBYGROUPNAME</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ENUM_DANHMUC.YEUCAUKCHINHSU</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8097,7 +11049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8107,6 +11059,10 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8145,6 +11101,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Is Lookup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Name/Group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lookup Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcoded/Filter Values</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8178,6 +11154,14 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8215,6 +11199,26 @@
           <t>Chanh an/Vien truong</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded nguoi khang nghi</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0=Chanh an; 1=Vien truong</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8248,6 +11252,26 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded cap khang nghi</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0=Cung cap; 1=Cap tren</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8285,6 +11309,26 @@
           <t>Khi trDVKN visible</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Don vi khang nghi</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Not found loaded in TaoHosoKC.aspx.cs</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Control exists but trDVKN visible=false; save only if trDVKN.Visible</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8318,6 +11362,14 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8351,6 +11403,14 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8384,6 +11444,26 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded loai khang nghi</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded in TaoHosoKC.aspx</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0=Ban an; 1=Quyet dinh</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8421,6 +11501,26 @@
           <t>ID ban an/quyet dinh</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>AHS_SOTHAM_BANAN or AHS_SOTHAM_QUYETDINH_VUAN</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>GSTPContext / AHS_SOTHAM_BL.AHS_ST_QD_VUAN_GETLIST</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>If rdbLoaiKN=0 load AHS_SOTHAM_BANAN by VUANID; if 1 load quyet dinh vu an</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8458,6 +11558,14 @@
           <t>Readonly</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8495,6 +11603,26 @@
           <t>Lay tu AHS_VUAN.TOAANID</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>DM_TOAAN / Session DONVIID depending field</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Court/unit ID</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8528,9 +11656,17 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>